--- a/artfynd/Karlstjärnberget artfynd.xlsx
+++ b/artfynd/Karlstjärnberget artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17225098</v>
+        <v>146193</v>
       </c>
       <c r="B2" t="n">
-        <v>91195</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -757,101 +757,68 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran # Picea abies</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99546396</v>
+        <v>153094</v>
       </c>
       <c r="B3" t="n">
-        <v>56852</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687007</v>
+        <v>687038</v>
       </c>
       <c r="R3" t="n">
-        <v>7090601</v>
+        <v>7089912</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,17 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,48 +862,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Jonas Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1895122</v>
+        <v>153095</v>
       </c>
       <c r="B4" t="n">
-        <v>79987</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687134</v>
+        <v>687036</v>
       </c>
       <c r="R4" t="n">
-        <v>7090019</v>
+        <v>7089938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>923941</v>
+        <v>6745812</v>
       </c>
       <c r="B5" t="n">
-        <v>90283</v>
+        <v>80298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>388</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687291</v>
+        <v>686964</v>
       </c>
       <c r="R5" t="n">
-        <v>7089967</v>
+        <v>7089898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,65 +1053,65 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>tallåga</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119665736</v>
+        <v>132839</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>80305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686900</v>
+        <v>686990</v>
       </c>
       <c r="R6" t="n">
-        <v>7090566</v>
+        <v>7089907</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,12 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,61 +1154,66 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119665738</v>
+        <v>332659</v>
       </c>
       <c r="B7" t="n">
-        <v>92527</v>
+        <v>96446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>1079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686920</v>
+        <v>686925</v>
       </c>
       <c r="R7" t="n">
-        <v>7090478</v>
+        <v>7090072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,12 +1240,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Asprik, tät och ganska bördig granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,48 +1261,53 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1999661</v>
+        <v>343951</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687038</v>
+        <v>686925</v>
       </c>
       <c r="R8" t="n">
-        <v>7090055</v>
+        <v>7090072</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,45 +1384,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87852</v>
+        <v>53408976</v>
       </c>
       <c r="B9" t="n">
-        <v>91506</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686724</v>
+        <v>686928</v>
       </c>
       <c r="R9" t="n">
-        <v>7090366</v>
+        <v>7090071</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,12 +1459,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2015-05-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2015-05-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,55 +1483,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>153095</v>
+        <v>589105</v>
       </c>
       <c r="B10" t="n">
-        <v>79012</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687036</v>
+        <v>687146</v>
       </c>
       <c r="R10" t="n">
-        <v>7089938</v>
+        <v>7089783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17225097</v>
+        <v>709586</v>
       </c>
       <c r="B11" t="n">
-        <v>79949</v>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,34 +1610,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>388</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687212</v>
+        <v>687154</v>
       </c>
       <c r="R11" t="n">
-        <v>7090356</v>
+        <v>7089910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,12 +1664,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,48 +1680,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asp # Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17225105</v>
+        <v>1594916</v>
       </c>
       <c r="B12" t="n">
-        <v>91256</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,34 +1707,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686925</v>
+        <v>687121</v>
       </c>
       <c r="R12" t="n">
-        <v>7090072</v>
+        <v>7090001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,12 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,83 +1777,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AN12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asp # Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119665735</v>
+        <v>1855470</v>
       </c>
       <c r="B13" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686899</v>
+        <v>687085</v>
       </c>
       <c r="R13" t="n">
-        <v>7090570</v>
+        <v>7089967</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,12 +1858,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,22 +1878,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1999659</v>
+        <v>2561422</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,34 +1901,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687304</v>
+        <v>687081</v>
       </c>
       <c r="R14" t="n">
-        <v>7090320</v>
+        <v>7089949</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,17 +1955,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Även korallblylav</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,31 +1971,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1999660</v>
+        <v>1977919</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,34 +1998,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687223</v>
+        <v>687117</v>
       </c>
       <c r="R15" t="n">
-        <v>7090364</v>
+        <v>7090012</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,17 +2052,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Även korallblylav</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,66 +2068,61 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1977924</v>
+        <v>1895122</v>
       </c>
       <c r="B16" t="n">
-        <v>78738</v>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687319</v>
+        <v>687134</v>
       </c>
       <c r="R16" t="n">
-        <v>7090008</v>
+        <v>7090019</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,12 +2149,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,31 +2165,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1084410</v>
+        <v>1999661</v>
       </c>
       <c r="B17" t="n">
-        <v>92045</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,37 +2192,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2014</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687215</v>
+        <v>687038</v>
       </c>
       <c r="R17" t="n">
-        <v>7089964</v>
+        <v>7090055</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2326,12 +2246,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,48 +2262,53 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132839</v>
+        <v>1999662</v>
       </c>
       <c r="B18" t="n">
-        <v>79956</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,13 +2318,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686990</v>
+        <v>687026</v>
       </c>
       <c r="R18" t="n">
-        <v>7089907</v>
+        <v>7090021</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,6 +2356,11 @@
           <t>2012-10-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Även bårdlav</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2442,7 +2372,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2460,10 +2390,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>153094</v>
+        <v>1999663</v>
       </c>
       <c r="B19" t="n">
-        <v>79012</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,34 +2401,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687038</v>
+        <v>686929</v>
       </c>
       <c r="R19" t="n">
-        <v>7089912</v>
+        <v>7089965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,12 +2455,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2541,26 +2471,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119665737</v>
+        <v>1999664</v>
       </c>
       <c r="B20" t="n">
-        <v>92527</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,34 +2503,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686909</v>
+        <v>686978</v>
       </c>
       <c r="R20" t="n">
-        <v>7090550</v>
+        <v>7090023</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,12 +2557,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,61 +2573,66 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1999664</v>
+        <v>133850979</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686978</v>
+        <v>687007</v>
       </c>
       <c r="R21" t="n">
-        <v>7090023</v>
+        <v>7090054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,12 +2659,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,66 +2680,61 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1594916</v>
+        <v>133850984</v>
       </c>
       <c r="B22" t="n">
-        <v>91210</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687121</v>
+        <v>687060</v>
       </c>
       <c r="R22" t="n">
-        <v>7090001</v>
+        <v>7090012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,12 +2761,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-85</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,57 +2786,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119665733</v>
+        <v>87852</v>
       </c>
       <c r="B23" t="n">
-        <v>92527</v>
+        <v>92183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686866</v>
+        <v>686724</v>
       </c>
       <c r="R23" t="n">
-        <v>7090569</v>
+        <v>7090366</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,12 +2863,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,26 +2879,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>589105</v>
+        <v>119665733</v>
       </c>
       <c r="B24" t="n">
-        <v>92551</v>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,34 +2911,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687146</v>
+        <v>686866</v>
       </c>
       <c r="R24" t="n">
-        <v>7089783</v>
+        <v>7090569</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,12 +2965,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3035,22 +2985,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>709586</v>
+        <v>119665737</v>
       </c>
       <c r="B25" t="n">
-        <v>92727</v>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3058,34 +3008,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687154</v>
+        <v>686909</v>
       </c>
       <c r="R25" t="n">
-        <v>7089910</v>
+        <v>7090550</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,12 +3062,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3132,57 +3082,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>17225106</v>
+        <v>119665738</v>
       </c>
       <c r="B26" t="n">
-        <v>95702</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1079</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>686925</v>
+        <v>686920</v>
       </c>
       <c r="R26" t="n">
-        <v>7090072</v>
+        <v>7090478</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,12 +3159,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3225,70 +3175,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asp # Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119665734</v>
+        <v>119665730</v>
       </c>
       <c r="B27" t="n">
-        <v>92535</v>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3226,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>686866</v>
+        <v>686899</v>
       </c>
       <c r="R27" t="n">
-        <v>7090569</v>
+        <v>7090583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,10 +3288,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2561422</v>
+        <v>119665734</v>
       </c>
       <c r="B28" t="n">
-        <v>78386</v>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3371,34 +3299,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687081</v>
+        <v>686866</v>
       </c>
       <c r="R28" t="n">
-        <v>7089949</v>
+        <v>7090569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,12 +3353,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3445,22 +3373,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119665731</v>
+        <v>119665735</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,21 +3396,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3492,10 +3420,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686843</v>
+        <v>686899</v>
       </c>
       <c r="R29" t="n">
-        <v>7090630</v>
+        <v>7090570</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3554,14 +3482,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1855478</v>
+        <v>119665731</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3585,14 +3513,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687085</v>
+        <v>686843</v>
       </c>
       <c r="R30" t="n">
-        <v>7089967</v>
+        <v>7090630</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3619,12 +3547,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3639,22 +3567,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119665728</v>
+        <v>99546396</v>
       </c>
       <c r="B31" t="n">
-        <v>91210</v>
+        <v>57144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,37 +3590,53 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>102613</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687193</v>
+        <v>687007</v>
       </c>
       <c r="R31" t="n">
-        <v>7090656</v>
+        <v>7090601</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3716,12 +3660,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2022-03-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3736,22 +3685,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Andreas Bernhold, Jonas Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>709587</v>
+        <v>119665729</v>
       </c>
       <c r="B32" t="n">
-        <v>92727</v>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,34 +3712,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687377</v>
+        <v>687061</v>
       </c>
       <c r="R32" t="n">
-        <v>7089978</v>
+        <v>7090542</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,12 +3766,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3833,22 +3786,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1977919</v>
+        <v>119665736</v>
       </c>
       <c r="B33" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,34 +3809,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Karltjärnsberget, Ång</t>
+          <t>Karlsbäck, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687117</v>
+        <v>686900</v>
       </c>
       <c r="R33" t="n">
-        <v>7090012</v>
+        <v>7090566</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,12 +3863,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2011-09-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3930,22 +3883,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1999663</v>
+        <v>923937</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>90932</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,34 +3906,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686929</v>
+        <v>687291</v>
       </c>
       <c r="R34" t="n">
-        <v>7089965</v>
+        <v>7089967</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,12 +3960,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4023,31 +3976,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1855466</v>
+        <v>1084410</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>92732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,21 +4003,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4027,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687192</v>
+        <v>687215</v>
       </c>
       <c r="R35" t="n">
-        <v>7089873</v>
+        <v>7089964</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4141,10 +4089,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17225102</v>
+        <v>1084413</v>
       </c>
       <c r="B36" t="n">
-        <v>79949</v>
+        <v>92732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4152,21 +4100,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>388</v>
+        <v>2014</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4176,10 +4124,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686964</v>
+        <v>687192</v>
       </c>
       <c r="R36" t="n">
-        <v>7089898</v>
+        <v>7089977</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,12 +4154,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,47 +4171,30 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>1 substratenheter # asp # Populus tremula</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1084413</v>
+        <v>709587</v>
       </c>
       <c r="B37" t="n">
-        <v>92045</v>
+        <v>91962</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4271,34 +4202,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2014</v>
+        <v>2079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>687192</v>
+        <v>687377</v>
       </c>
       <c r="R37" t="n">
-        <v>7089977</v>
+        <v>7089978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4325,12 +4256,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4341,69 +4272,64 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>asplåga</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>17225100</v>
+        <v>1855466</v>
       </c>
       <c r="B38" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>687026</v>
+        <v>687192</v>
       </c>
       <c r="R38" t="n">
-        <v>7090021</v>
+        <v>7089873</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4427,12 +4353,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4443,48 +4369,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AN38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>3 substratenheter # asp # Populus tremula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>14917244</v>
+        <v>1977915</v>
       </c>
       <c r="B39" t="n">
-        <v>5492</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,39 +4396,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>687346</v>
+        <v>687539</v>
       </c>
       <c r="R39" t="n">
-        <v>7089996</v>
+        <v>7089905</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,22 +4450,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4581,57 +4470,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1895125</v>
+        <v>1977918</v>
       </c>
       <c r="B40" t="n">
-        <v>79987</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Karlstjärnberget, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>687357</v>
+        <v>687319</v>
       </c>
       <c r="R40" t="n">
-        <v>7090012</v>
+        <v>7090008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,12 +4547,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4674,66 +4563,61 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119665729</v>
+        <v>1895121</v>
       </c>
       <c r="B41" t="n">
-        <v>78739</v>
+        <v>80336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687061</v>
+        <v>687291</v>
       </c>
       <c r="R41" t="n">
-        <v>7090542</v>
+        <v>7089968</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,12 +4644,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4780,22 +4664,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1895121</v>
+        <v>1895123</v>
       </c>
       <c r="B42" t="n">
-        <v>79987</v>
+        <v>80336</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4827,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687291</v>
+        <v>687357</v>
       </c>
       <c r="R42" t="n">
-        <v>7089967</v>
+        <v>7090012</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,10 +4773,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14917245</v>
+        <v>14917244</v>
       </c>
       <c r="B43" t="n">
-        <v>5492</v>
+        <v>5495</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4929,10 +4813,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687349</v>
+        <v>687346</v>
       </c>
       <c r="R43" t="n">
-        <v>7090001</v>
+        <v>7089996</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4962,19 +4846,9 @@
           <t>2011-09-18</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5001,55 +4875,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>53408976</v>
+        <v>14917245</v>
       </c>
       <c r="B44" t="n">
-        <v>91256</v>
+        <v>5495</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1205</v>
+        <v>101410</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Karltjärnberget, Ång</t>
+          <t>Karlstjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686928</v>
+        <v>687349</v>
       </c>
       <c r="R44" t="n">
-        <v>7090071</v>
+        <v>7090001</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,22 +4945,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5100,29 +4959,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119665730</v>
+        <v>6461220</v>
       </c>
       <c r="B45" t="n">
-        <v>92529</v>
+        <v>79085</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5130,34 +4988,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Karlsbäck, Ång</t>
+          <t>Karltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>686899</v>
+        <v>687539</v>
       </c>
       <c r="R45" t="n">
-        <v>7090583</v>
+        <v>7089905</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,12 +5042,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2011-09-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5204,15 +5062,428 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>6745811</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80298</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>388</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Karlstjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>687212</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7090356</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2012-10-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2012-10-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>119665728</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Karlsbäck, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>687193</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7090656</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>Hanna Bäckman</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>Hanna Bäckman</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1999659</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Karlstjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>687304</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7090320</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2012-10-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2012-10-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Även korallblylav</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1999660</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Karlstjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>687223</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7090364</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2012-10-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2012-10-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Även korallblylav</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
